--- a/evaluation/rouge/evaluation_table.xlsx
+++ b/evaluation/rouge/evaluation_table.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="41">
   <si>
     <t>No</t>
   </si>
@@ -49,241 +49,94 @@
     <t>Rata-rata</t>
   </si>
   <si>
-    <t>45.00%</t>
-  </si>
-  <si>
-    <t>40.00%</t>
+    <t>69.23%</t>
   </si>
   <si>
     <t>100.00%</t>
   </si>
   <si>
-    <t>8.11%</t>
-  </si>
-  <si>
-    <t>2.70%</t>
-  </si>
-  <si>
-    <t>5.33%</t>
-  </si>
-  <si>
-    <t>42.31%</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>72.50%</t>
-  </si>
-  <si>
-    <t>3.05%</t>
-  </si>
-  <si>
-    <t>10.34%</t>
-  </si>
-  <si>
-    <t>13.79%</t>
-  </si>
-  <si>
-    <t>10.67%</t>
-  </si>
-  <si>
-    <t>26.61%</t>
+    <t>71.43%</t>
+  </si>
+  <si>
+    <t>75.00%</t>
+  </si>
+  <si>
+    <t>76.47%</t>
+  </si>
+  <si>
+    <t>80.95%</t>
+  </si>
+  <si>
+    <t>87.88%</t>
+  </si>
+  <si>
+    <t>60.00%</t>
+  </si>
+  <si>
+    <t>63.64%</t>
+  </si>
+  <si>
+    <t>80.00%</t>
+  </si>
+  <si>
+    <t>76.02%</t>
+  </si>
+  <si>
+    <t>81.82%</t>
+  </si>
+  <si>
+    <t>83.33%</t>
+  </si>
+  <si>
+    <t>85.71%</t>
+  </si>
+  <si>
+    <t>86.67%</t>
+  </si>
+  <si>
+    <t>89.47%</t>
+  </si>
+  <si>
+    <t>93.55%</t>
+  </si>
+  <si>
+    <t>77.78%</t>
   </si>
   <si>
     <t>88.89%</t>
   </si>
   <si>
-    <t>30.00%</t>
-  </si>
-  <si>
-    <t>8.33%</t>
-  </si>
-  <si>
-    <t>30.77%</t>
+    <t>86.07%</t>
+  </si>
+  <si>
+    <t>66.67%</t>
+  </si>
+  <si>
+    <t>73.33%</t>
+  </si>
+  <si>
+    <t>87.50%</t>
+  </si>
+  <si>
+    <t>55.56%</t>
+  </si>
+  <si>
+    <t>78.95%</t>
+  </si>
+  <si>
+    <t>74.23%</t>
   </si>
   <si>
     <t>84.62%</t>
   </si>
   <si>
-    <t>91.67%</t>
-  </si>
-  <si>
-    <t>33.33%</t>
-  </si>
-  <si>
-    <t>50.00%</t>
-  </si>
-  <si>
-    <t>57.14%</t>
-  </si>
-  <si>
-    <t>25.00%</t>
-  </si>
-  <si>
-    <t>56.65%</t>
-  </si>
-  <si>
-    <t>62.07%</t>
-  </si>
-  <si>
-    <t>55.17%</t>
-  </si>
-  <si>
-    <t>12.77%</t>
-  </si>
-  <si>
-    <t>4.08%</t>
-  </si>
-  <si>
-    <t>9.09%</t>
-  </si>
-  <si>
-    <t>56.41%</t>
-  </si>
-  <si>
-    <t>57.89%</t>
-  </si>
-  <si>
-    <t>84.06%</t>
-  </si>
-  <si>
-    <t>5.59%</t>
-  </si>
-  <si>
-    <t>17.14%</t>
-  </si>
-  <si>
-    <t>22.22%</t>
-  </si>
-  <si>
-    <t>5.44%</t>
-  </si>
-  <si>
-    <t>17.58%</t>
-  </si>
-  <si>
-    <t>33.97%</t>
-  </si>
-  <si>
-    <t>42.11%</t>
-  </si>
-  <si>
-    <t>31.58%</t>
-  </si>
-  <si>
-    <t>1.35%</t>
-  </si>
-  <si>
-    <t>32.00%</t>
-  </si>
-  <si>
-    <t>71.79%</t>
-  </si>
-  <si>
-    <t>7.14%</t>
-  </si>
-  <si>
-    <t>3.57%</t>
-  </si>
-  <si>
-    <t>21.62%</t>
-  </si>
-  <si>
-    <t>75.00%</t>
-  </si>
-  <si>
-    <t>66.67%</t>
-  </si>
-  <si>
-    <t>72.73%</t>
-  </si>
-  <si>
-    <t>16.67%</t>
-  </si>
-  <si>
-    <t>13.33%</t>
-  </si>
-  <si>
-    <t>39.52%</t>
-  </si>
-  <si>
-    <t>59.26%</t>
-  </si>
-  <si>
-    <t>44.44%</t>
-  </si>
-  <si>
-    <t>2.33%</t>
-  </si>
-  <si>
-    <t>43.24%</t>
-  </si>
-  <si>
-    <t>83.58%</t>
-  </si>
-  <si>
-    <t>12.12%</t>
-  </si>
-  <si>
-    <t>5.88%</t>
-  </si>
-  <si>
-    <t>4.49%</t>
-  </si>
-  <si>
-    <t>26.65%</t>
-  </si>
-  <si>
-    <t>5.41%</t>
-  </si>
-  <si>
-    <t>4.00%</t>
-  </si>
-  <si>
-    <t>34.62%</t>
-  </si>
-  <si>
-    <t>8.00%</t>
-  </si>
-  <si>
-    <t>23.99%</t>
-  </si>
-  <si>
-    <t>20.00%</t>
-  </si>
-  <si>
-    <t>23.08%</t>
-  </si>
-  <si>
-    <t>69.23%</t>
-  </si>
-  <si>
-    <t>42.86%</t>
-  </si>
-  <si>
-    <t>37.50%</t>
-  </si>
-  <si>
-    <t>49.51%</t>
-  </si>
-  <si>
-    <t>41.38%</t>
-  </si>
-  <si>
-    <t>8.51%</t>
-  </si>
-  <si>
-    <t>6.82%</t>
-  </si>
-  <si>
-    <t>46.15%</t>
-  </si>
-  <si>
-    <t>13.19%</t>
-  </si>
-  <si>
-    <t>30.21%</t>
+    <t>93.33%</t>
+  </si>
+  <si>
+    <t>88.24%</t>
+  </si>
+  <si>
+    <t>84.81%</t>
   </si>
 </sst>
 </file>
@@ -684,28 +537,28 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -713,31 +566,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -745,31 +598,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -777,31 +630,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -809,31 +662,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -841,31 +694,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -873,31 +726,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -905,31 +758,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -937,31 +790,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -969,31 +822,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1001,31 +854,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1033,31 +886,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1065,31 +918,31 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="J14" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1100,28 +953,28 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H15" t="s">
         <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1129,31 +982,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H16" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="J16" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1161,31 +1014,31 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="J17" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
